--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.146.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.146.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.146.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.146.xlsx
@@ -422,18 +422,18 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="41" customWidth="1" min="14" max="14"/>
-    <col width="42" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.146.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.146.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0146.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0146.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -607,18 +607,18 @@
           <t>L127: line starts with digit/letter garbage token | suspicious token(s): 1decree (letter/digit mix) :: 1decree made under the provisions of the 77th Order of the Parties may be</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L106: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: subpo Ã¦ enaed</t>
-        </is>
-      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L30: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: following :â€”</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]139</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]139</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L30: isolated marker/symbol line :: 139</t>
@@ -626,7 +626,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L118: isolated marker/symbol line :: a.)</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]139</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -661,7 +661,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -683,7 +683,11 @@
           <t>L75: isolated marker/symbol line :: G</t>
         </is>
       </c>
-      <c r="O3" s="1" t="inlineStr"/>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>L118: isolated marker/symbol line :: a.)</t>
+        </is>
+      </c>
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr"/>
       <c r="R3" s="1" t="inlineStr"/>
@@ -750,7 +754,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -957,7 +961,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -1001,7 +1005,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1040,7 +1044,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
